--- a/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
+++ b/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\douwe\AE4115-23_EXPERIMENTAL SIMULATIONS\Group_15_Redo_BAL\CORRECTIONS_FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DA9C92-F4BE-4115-8B20-5F0F9B076CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA95E40D-39FF-4AE9-AD07-44F3B22310F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
   </bookViews>
   <sheets>
     <sheet name="solid_body_blockage" sheetId="1" r:id="rId1"/>
@@ -1389,15 +1389,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1446,10 +1437,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2164,23 +2164,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
     </row>
     <row r="2" spans="1:15" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
@@ -2230,27 +2230,27 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="81" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="85" t="s">
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="82" t="s">
         <v>139</v>
       </c>
-      <c r="J3" s="86"/>
-      <c r="K3" s="86"/>
-      <c r="L3" s="86"/>
-      <c r="M3" s="86"/>
-      <c r="N3" s="78" t="s">
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="75" t="s">
         <v>140</v>
       </c>
-      <c r="O3" s="80"/>
+      <c r="O3" s="77"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
@@ -2397,27 +2397,27 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="80" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
-      <c r="D7" s="84"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="76" t="s">
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="87"/>
-      <c r="N7" s="78" t="s">
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="75" t="s">
         <v>140</v>
       </c>
-      <c r="O7" s="79"/>
+      <c r="O7" s="76"/>
     </row>
     <row r="8" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
@@ -2517,27 +2517,27 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="83" t="s">
+      <c r="A10" s="80" t="s">
         <v>124</v>
       </c>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="84"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="84"/>
-      <c r="H10" s="84"/>
-      <c r="I10" s="76" t="s">
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="J10" s="77"/>
-      <c r="K10" s="77"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="77"/>
-      <c r="N10" s="78" t="s">
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="74"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="75" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="79"/>
+      <c r="O10" s="76"/>
     </row>
     <row r="11" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
@@ -2643,21 +2643,21 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
-      <c r="E17" s="81" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+      <c r="E17" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="I17" s="81" t="s">
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="I17" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
     </row>
     <row r="18" spans="1:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
@@ -2816,15 +2816,15 @@
       <c r="F25" s="59"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="69" t="s">
         <v>157</v>
       </c>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
     </row>
     <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
@@ -3093,11 +3093,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="78" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
     </row>
     <row r="3" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
@@ -3157,11 +3157,11 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="81" t="s">
+      <c r="A21" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
     </row>
     <row r="22" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
@@ -3235,46 +3235,47 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="89" t="s">
+      <c r="A3" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="88"/>
-      <c r="C3" s="88"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>0.1065</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="89"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>0.8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>0.1085</v>
       </c>
     </row>
@@ -3521,11 +3522,11 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="85" t="s">
         <v>168</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
     </row>
     <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -3561,11 +3562,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="71"/>
-      <c r="C7" s="71"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
     </row>
     <row r="8" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">

--- a/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
+++ b/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
@@ -8,21 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\douwe\AE4115-23_EXPERIMENTAL SIMULATIONS\Group_15_Redo_BAL\CORRECTIONS_FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA95E40D-39FF-4AE9-AD07-44F3B22310F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A64CD6-42A4-485F-88D3-49D5D8B708E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
   </bookViews>
   <sheets>
     <sheet name="solid_body_blockage" sheetId="1" r:id="rId1"/>
-    <sheet name="correction_factors" sheetId="11" r:id="rId2"/>
-    <sheet name="PROP" sheetId="2" r:id="rId3"/>
-    <sheet name="WING" sheetId="4" r:id="rId4"/>
-    <sheet name="tail_correction" sheetId="10" r:id="rId5"/>
-    <sheet name="FUSELAGE" sheetId="5" r:id="rId6"/>
-    <sheet name="HORIZONTAL_TAIL" sheetId="6" r:id="rId7"/>
-    <sheet name="VERTICAL_TAIL" sheetId="7" r:id="rId8"/>
-    <sheet name="TUNNEL" sheetId="8" r:id="rId9"/>
-    <sheet name="STRUTS" sheetId="9" r:id="rId10"/>
+    <sheet name="PROP" sheetId="2" r:id="rId2"/>
+    <sheet name="WING" sheetId="4" r:id="rId3"/>
+    <sheet name="tail_correction" sheetId="10" r:id="rId4"/>
+    <sheet name="FUSELAGE" sheetId="5" r:id="rId5"/>
+    <sheet name="HORIZONTAL_TAIL" sheetId="6" r:id="rId6"/>
+    <sheet name="VERTICAL_TAIL" sheetId="7" r:id="rId7"/>
+    <sheet name="TUNNEL" sheetId="8" r:id="rId8"/>
+    <sheet name="STRUTS" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="174">
   <si>
     <t>Body</t>
   </si>
@@ -567,12 +566,6 @@
   </si>
   <si>
     <t>dCm_0.25c / da_t</t>
-  </si>
-  <si>
-    <t>tau_2</t>
-  </si>
-  <si>
-    <t>delta</t>
   </si>
 </sst>
 </file>
@@ -622,7 +615,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,12 +682,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="45">
     <border>
@@ -1285,7 +1272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1444,12 +1431,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3087,209 +3068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{390E4474-71C3-4371-935C-8F12FA2B8A53}">
-  <dimension ref="A2:C26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="78" t="s">
-        <v>143</v>
-      </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="4">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B5" s="3">
-        <f>67.829</f>
-        <v>67.828999999999994</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="3">
-        <f>B4/B5</f>
-        <v>0.24915596573736898</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3">
-        <v>700</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="78" t="s">
-        <v>148</v>
-      </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-    </row>
-    <row r="22" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="B23" s="4">
-        <v>20</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" s="3">
-        <v>70</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="3">
-        <f>B23/B24</f>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="3">
-        <v>610</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>146</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8943DE28-C728-43E4-B8C0-984BD3614D93}">
-  <dimension ref="A2:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="88" t="s">
-        <v>168</v>
-      </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B4" s="1">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.1065</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="88" t="s">
-        <v>169</v>
-      </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.1085</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:C5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DE3999-9250-4D69-A070-2D4E6C21A0D3}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3343,7 +3122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B3ACAF9-5330-4D80-8205-C3B2F3F18559}">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3501,7 +3280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78CBAC62-2666-4A5D-80B9-0D82AF074AF3}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3629,7 +3408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA935838-9803-4D28-BB5F-9527F2166E9C}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3691,7 +3470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48C65C0-CE32-4736-962B-594A33BDB19E}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3857,7 +3636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CED5ACF-DC54-43BC-95C8-1A622F1EFA29}">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4007,7 +3786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{168CB0EA-C8E2-45E5-AB6B-358E6234C580}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4100,4 +3879,146 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{390E4474-71C3-4371-935C-8F12FA2B8A53}">
+  <dimension ref="A2:C26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="4">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="3">
+        <f>67.829</f>
+        <v>67.828999999999994</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="3">
+        <f>B4/B5</f>
+        <v>0.24915596573736898</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>700</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="78" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+    </row>
+    <row r="22" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="4">
+        <v>20</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="3">
+        <v>70</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="3">
+        <f>B23/B24</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3">
+        <v>610</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A21:C21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
+++ b/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\douwe\AE4115-23_EXPERIMENTAL SIMULATIONS\Group_15_Redo_BAL\CORRECTIONS_FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A64CD6-42A4-485F-88D3-49D5D8B708E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B20DE75-B6E1-453A-808E-7327CB231831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
+    <workbookView xWindow="-28920" yWindow="1635" windowWidth="29040" windowHeight="15720" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
   </bookViews>
   <sheets>
     <sheet name="solid_body_blockage" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="175">
   <si>
     <t>Body</t>
   </si>
@@ -566,6 +566,9 @@
   </si>
   <si>
     <t>dCm_0.25c / da_t</t>
+  </si>
+  <si>
+    <t>OLD</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1433,6 +1436,7 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1455,16 +1459,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>302837</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>469525</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>116477</xdr:rowOff>
+      <xdr:rowOff>164102</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>264874</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>168547</xdr:rowOff>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>431562</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>29482</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1493,8 +1497,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14933237" y="301534"/>
-          <a:ext cx="5448437" cy="5914209"/>
+          <a:off x="27472900" y="354602"/>
+          <a:ext cx="5534162" cy="5961380"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1505,16 +1509,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>413657</xdr:colOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>316502</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>16328</xdr:rowOff>
+      <xdr:rowOff>115388</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>592038</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>171615</xdr:rowOff>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>492978</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>72555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1543,8 +1547,108 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15044057" y="6678385"/>
-          <a:ext cx="8716591" cy="5148020"/>
+          <a:off x="26081627" y="7163888"/>
+          <a:ext cx="8844226" cy="5291167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>153489</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>184104</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>456263</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>109127</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EFA15E0-AE43-CDF4-DA21-D4FB7BA95CA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15393489" y="755604"/>
+          <a:ext cx="10827899" cy="4497023"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>133399</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>149319</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>506544</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>106235</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{920B581B-05C0-6383-954B-CF544A40FF4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14135149" y="7578819"/>
+          <a:ext cx="10898270" cy="4338416"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2127,7 +2231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E3BC68-AA17-4FD3-A537-743FAC90C685}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" customWidth="1"/>
@@ -2144,7 +2248,7 @@
     <col min="15" max="15" width="18.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="71" t="s">
         <v>160</v>
       </c>
@@ -2163,7 +2267,7 @@
       <c r="N1" s="72"/>
       <c r="O1" s="72"/>
     </row>
-    <row r="2" spans="1:15" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -2210,7 +2314,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="15.6" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="81" t="s">
         <v>125</v>
       </c>
@@ -2232,8 +2336,11 @@
         <v>140</v>
       </c>
       <c r="O3" s="77"/>
-    </row>
-    <row r="4" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="P3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
@@ -2275,13 +2382,16 @@
         <v>1.43</v>
       </c>
       <c r="N4" s="41">
-        <v>1.02</v>
+        <v>1.01892</v>
       </c>
       <c r="O4" s="2">
+        <v>0.88170000000000004</v>
+      </c>
+      <c r="P4">
         <v>0.875</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>3</v>
       </c>
@@ -2323,13 +2433,16 @@
         <v>1.43</v>
       </c>
       <c r="N5" s="29">
-        <v>1.02</v>
+        <v>1.01892</v>
       </c>
       <c r="O5" s="1">
+        <v>0.85892999999999997</v>
+      </c>
+      <c r="P5" s="88">
         <v>0.86250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>4</v>
       </c>
@@ -2371,13 +2484,16 @@
         <v>1.43</v>
       </c>
       <c r="N6" s="42">
-        <v>1.03833</v>
+        <v>1.03667</v>
       </c>
       <c r="O6" s="7">
+        <v>0.85914999999999997</v>
+      </c>
+      <c r="P6">
         <v>0.86199999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80" t="s">
         <v>123</v>
       </c>
@@ -2400,7 +2516,7 @@
       </c>
       <c r="O7" s="76"/>
     </row>
-    <row r="8" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>2</v>
       </c>
@@ -2442,13 +2558,16 @@
         <v>1.43</v>
       </c>
       <c r="N8" s="41">
-        <v>0.91</v>
+        <v>0.90954000000000002</v>
       </c>
       <c r="O8" s="2">
+        <v>0.86121999999999999</v>
+      </c>
+      <c r="P8" s="88">
         <v>0.86250000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>156</v>
       </c>
@@ -2491,13 +2610,16 @@
         <v>1.43</v>
       </c>
       <c r="N9" s="42">
-        <v>0.93330000000000002</v>
+        <v>0.93350999999999995</v>
       </c>
       <c r="O9" s="7">
+        <v>0.86121999999999999</v>
+      </c>
+      <c r="P9" s="88">
         <v>0.86250000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="80" t="s">
         <v>124</v>
       </c>
@@ -2520,7 +2642,7 @@
       </c>
       <c r="O10" s="76"/>
     </row>
-    <row r="11" spans="1:15" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>159</v>
       </c>
@@ -2569,10 +2691,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="O11" s="2">
+        <v>0.85911999999999999</v>
+      </c>
+      <c r="P11">
         <v>0.86250000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>6</v>
       </c>
@@ -2620,6 +2745,9 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="O12" s="1">
+        <v>0.85987999999999998</v>
+      </c>
+      <c r="P12">
         <v>0.86250000000000004</v>
       </c>
     </row>
@@ -2843,11 +2971,11 @@
       </c>
       <c r="D28" s="2">
         <f t="shared" ref="D28:E30" si="1">N4</f>
-        <v>1.02</v>
+        <v>1.01892</v>
       </c>
       <c r="E28" s="2">
         <f t="shared" si="1"/>
-        <v>0.875</v>
+        <v>0.88170000000000004</v>
       </c>
       <c r="F28" s="26">
         <f>$B$22</f>
@@ -2855,7 +2983,7 @@
       </c>
       <c r="G28" s="58">
         <f>C28*(D28*E28*B28)/(F28^1.5)</f>
-        <v>9.0589213101597383E-4</v>
+        <v>9.1186215199534984E-4</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -2871,11 +2999,11 @@
       </c>
       <c r="D29" s="1">
         <f t="shared" si="1"/>
-        <v>1.02</v>
+        <v>1.01892</v>
       </c>
       <c r="E29" s="1">
         <f t="shared" si="1"/>
-        <v>0.86250000000000004</v>
+        <v>0.85892999999999997</v>
       </c>
       <c r="F29" s="56">
         <f t="shared" ref="F29:F34" si="2">$B$22</f>
@@ -2883,7 +3011,7 @@
       </c>
       <c r="G29" s="29">
         <f t="shared" ref="G29:G34" si="3">C29*(D29*E29*B29)/(F29^1.5)</f>
-        <v>2.88040073958326E-4</v>
+        <v>2.865441172809803E-4</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -2899,11 +3027,11 @@
       </c>
       <c r="D30" s="1">
         <f t="shared" si="1"/>
-        <v>1.03833</v>
+        <v>1.03667</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="1"/>
-        <v>0.86199999999999999</v>
+        <v>0.85914999999999997</v>
       </c>
       <c r="F30" s="56">
         <f t="shared" si="2"/>
@@ -2911,7 +3039,7 @@
       </c>
       <c r="G30" s="29">
         <f t="shared" si="3"/>
-        <v>1.0656777073516555E-4</v>
+        <v>1.060456206576917E-4</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -2927,11 +3055,11 @@
       </c>
       <c r="D31" s="1">
         <f>N8</f>
-        <v>0.91</v>
+        <v>0.90954000000000002</v>
       </c>
       <c r="E31" s="1">
         <f>O8</f>
-        <v>0.86250000000000004</v>
+        <v>0.86121999999999999</v>
       </c>
       <c r="F31" s="56">
         <f t="shared" si="2"/>
@@ -2939,7 +3067,7 @@
       </c>
       <c r="G31" s="29">
         <f t="shared" si="3"/>
-        <v>4.2332804856281391E-3</v>
+        <v>4.2248613276898899E-3</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -2955,11 +3083,11 @@
       </c>
       <c r="D32" s="1">
         <f>N9</f>
-        <v>0.93330000000000002</v>
+        <v>0.93350999999999995</v>
       </c>
       <c r="E32" s="1">
         <f>O9</f>
-        <v>0.86250000000000004</v>
+        <v>0.86121999999999999</v>
       </c>
       <c r="F32" s="56">
         <f t="shared" si="2"/>
@@ -2967,7 +3095,7 @@
       </c>
       <c r="G32" s="29">
         <f t="shared" si="3"/>
-        <v>4.2818836316867371E-4</v>
+        <v>4.2764910965506671E-4</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2987,7 +3115,7 @@
       </c>
       <c r="E33" s="1">
         <f>O11</f>
-        <v>0.86250000000000004</v>
+        <v>0.85911999999999999</v>
       </c>
       <c r="F33" s="56">
         <f t="shared" si="2"/>
@@ -2995,7 +3123,7 @@
       </c>
       <c r="G33" s="29">
         <f t="shared" si="3"/>
-        <v>1.1244023936686617E-3</v>
+        <v>1.1199960399404297E-3</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3015,7 +3143,7 @@
       </c>
       <c r="E34" s="1">
         <f>O12</f>
-        <v>0.86250000000000004</v>
+        <v>0.85987999999999998</v>
       </c>
       <c r="F34" s="28">
         <f t="shared" si="2"/>
@@ -3023,7 +3151,7 @@
       </c>
       <c r="G34" s="60">
         <f t="shared" si="3"/>
-        <v>1.4306695234491047E-4</v>
+        <v>1.4263236055923664E-4</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3032,7 +3160,7 @@
       </c>
       <c r="G35" s="62">
         <f>SUM(G28:G34)</f>
-        <v>7.2294381705198503E-3</v>
+        <v>7.2195907277786435E-3</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -3042,7 +3170,7 @@
       </c>
       <c r="G37" s="64">
         <f>G28+G31+G33+G34</f>
-        <v>6.4066419626576856E-3</v>
+        <v>6.399351880184906E-3</v>
       </c>
     </row>
   </sheetData>

--- a/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
+++ b/CORRECTIONS_FINAL/CORRECTIONS_SHEET.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\douwe\AE4115-23_EXPERIMENTAL SIMULATIONS\Group_15_Redo_BAL\CORRECTIONS_FINAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B20DE75-B6E1-453A-808E-7327CB231831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039C9DE4-CDE6-4A9D-AF6A-E2E4213F91D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1635" windowWidth="29040" windowHeight="15720" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{6779DE78-6A77-4C37-B946-ECD2BA7E5752}"/>
   </bookViews>
   <sheets>
     <sheet name="solid_body_blockage" sheetId="1" r:id="rId1"/>
@@ -1275,7 +1275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1436,7 +1436,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2438,7 +2437,7 @@
       <c r="O5" s="1">
         <v>0.85892999999999997</v>
       </c>
-      <c r="P5" s="88">
+      <c r="P5">
         <v>0.86250000000000004</v>
       </c>
     </row>
@@ -2563,7 +2562,7 @@
       <c r="O8" s="2">
         <v>0.86121999999999999</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8">
         <v>0.86250000000000004</v>
       </c>
     </row>
@@ -2615,7 +2614,7 @@
       <c r="O9" s="7">
         <v>0.86121999999999999</v>
       </c>
-      <c r="P9" s="88">
+      <c r="P9">
         <v>0.86250000000000004</v>
       </c>
     </row>
